--- a/artfynd/A 36895-2024 artfynd.xlsx
+++ b/artfynd/A 36895-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137294708</v>
       </c>
       <c r="B2" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1141,6 +1141,123 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137294706</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137329946</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58137</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blåbärsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>756070</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7174764</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329946</t>
         </is>
       </c>
     </row>
@@ -1150,6 +1267,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36895-2024 artfynd.xlsx
+++ b/artfynd/A 36895-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137294708</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137294707</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137294705</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137294706</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>137329946</v>
       </c>
       <c r="B6" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 36895-2024 artfynd.xlsx
+++ b/artfynd/A 36895-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137294708</v>
       </c>
       <c r="B2" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36895-2024 artfynd.xlsx
+++ b/artfynd/A 36895-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137294708</v>
       </c>
       <c r="B2" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137294707</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,52 +904,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137294705</v>
+        <v>137395041</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sittuträsk, Vb</t>
+          <t>Sittuberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756103</v>
+        <v>756118</v>
       </c>
       <c r="R4" t="n">
-        <v>7174750</v>
+        <v>7174792</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,27 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:49</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,75 +990,79 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294705</t>
+          <t>https://artportalen.se/Sighting/137395041</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137294706</v>
+        <v>137395046</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sittuträsk, Vb</t>
+          <t>Sittuberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756120</v>
+        <v>756114</v>
       </c>
       <c r="R5" t="n">
-        <v>7174748</v>
+        <v>7174737</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,27 +1086,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,71 +1100,79 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294706</t>
+          <t>https://artportalen.se/Sighting/137395046</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137329946</v>
+        <v>137395075</v>
       </c>
       <c r="B6" t="n">
-        <v>58138</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåbärsliden, Vb</t>
+          <t>Sittuberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756070</v>
+        <v>756041</v>
       </c>
       <c r="R6" t="n">
-        <v>7174764</v>
+        <v>7174663</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,27 +1196,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,22 +1210,829 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137395075</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137395198</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sittuberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>756042</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7174722</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137395198</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137395084</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80636</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sittuberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>755985</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7174686</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på sälg</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137395084</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137294705</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sittuträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>756103</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7174750</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294705</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137294706</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sittuträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>756120</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7174748</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294706</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137395025</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sittuberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>756101</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7174750</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137395025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137395072</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sittuberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>756114</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7174737</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137395072</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137329946</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58139</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Blåbärsliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>756070</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7174764</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137329946</t>
         </is>
@@ -1268,6 +2045,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36895-2024 artfynd.xlsx
+++ b/artfynd/A 36895-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137294708</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137294707</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137395041</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137395046</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137395075</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137395198</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137395084</v>
       </c>
       <c r="B8" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36895-2024 artfynd.xlsx
+++ b/artfynd/A 36895-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137294708</v>
       </c>
       <c r="B2" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137294707</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137395041</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137395046</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137395075</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137395198</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137395084</v>
       </c>
       <c r="B8" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36895-2024 artfynd.xlsx
+++ b/artfynd/A 36895-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137294708</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137294707</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137395041</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137395046</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137395075</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137395198</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137395084</v>
       </c>
       <c r="B8" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36895-2024 artfynd.xlsx
+++ b/artfynd/A 36895-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137294708</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137294707</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137395041</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137395046</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137395075</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137395198</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137395084</v>
       </c>
       <c r="B8" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137294705</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>137294706</v>
       </c>
       <c r="B10" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>137395025</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137395072</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>137329946</v>
       </c>
       <c r="B13" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
